--- a/conformance/cases/xlsx-06-hidden-and-merged.xlsx
+++ b/conformance/cases/xlsx-06-hidden-and-merged.xlsx
@@ -13,7 +13,7 @@
     <row r="1" hidden="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiêu đề</t>
+          <t xml:space="preserve">Title</t>
         </is>
       </c>
     </row>
@@ -96,7 +96,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bắt đầu</t>
+          <t xml:space="preserve">Start</t>
         </is>
       </c>
     </row>
@@ -113,7 +113,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">gửi yêu cầu</t>
+          <t xml:space="preserve">send request</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -140,7 +140,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xử lý</t>
+          <t xml:space="preserve">Process</t>
         </is>
       </c>
     </row>
@@ -179,7 +179,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xong</t>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
     </row>
